--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F444F9-C86C-2749-9DC2-F05C3966481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D010587A-D445-D543-B783-C387F3428A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
   <si>
     <t>blank</t>
   </si>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>quiring, quire and folio numbers, ruling, pricking, VisColl</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>ComSt handbook, YT video</t>
@@ -255,22 +252,40 @@
     <t>Collect your notes and questions from the course.</t>
   </si>
   <si>
-    <t>closeup of parchment</t>
-  </si>
-  <si>
-    <t>closeup of papyrus</t>
-  </si>
-  <si>
-    <t>multi-column manuscript</t>
-  </si>
-  <si>
-    <t>quill, etc.</t>
-  </si>
-  <si>
-    <t>red rubrics &amp; annotations</t>
-  </si>
-  <si>
-    <t>manuscript index?</t>
+    <t>book-binding-front.jpg</t>
+  </si>
+  <si>
+    <t>bible-gutenberg.jpg</t>
+  </si>
+  <si>
+    <t>parchment-bcuf-L2057_089v.jpg</t>
+  </si>
+  <si>
+    <t>papyrus-growing.jpg</t>
+  </si>
+  <si>
+    <t>interlinear-sbb-diez-A-oct-160-f002r.jpg</t>
+  </si>
+  <si>
+    <t>book-open-pages-closeup.jpg</t>
+  </si>
+  <si>
+    <t>pen-qalam.jpg</t>
+  </si>
+  <si>
+    <t>rubrics-sbb-ms-or-quart-887-p001.jpg</t>
+  </si>
+  <si>
+    <t>bible-hebrew.jpg</t>
+  </si>
+  <si>
+    <t>books-around-door.jpg</t>
+  </si>
+  <si>
+    <t>BNF-arabe-14-f002v-003r.jpg</t>
+  </si>
+  <si>
+    <t>[gruendlerIntroduction2020, vallejomoreuBooksSkinDetectives2023]</t>
   </si>
 </sst>
 </file>
@@ -282,9 +297,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -376,20 +398,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -399,35 +421,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -834,22 +857,22 @@
         <v>40</v>
       </c>
       <c r="I2" t="str">
-        <f>B2 &amp; ". " &amp; E2 &amp; ": " &amp; G2</f>
-        <v>1. Introduction: The physical side of scriptures</v>
+        <f>B2 &amp; ". " &amp; E2 &amp; IF(EXACT(E2,F2),,": " &amp; F2)</f>
+        <v>1. Introduction</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" ref="J2:J15" si="1">B2</f>
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Introduction</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -886,6 +909,10 @@
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="17"/>
+      <c r="I3" s="13" t="str">
+        <f t="shared" ref="I3:I15" si="4">B3 &amp; ". " &amp; E3 &amp; IF(EXACT(E3,F3),,": " &amp; F3)</f>
+        <v>. Labor Day (no class)</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="N3" s="18"/>
     </row>
@@ -913,28 +940,28 @@
         <v>41</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4:I15" si="4">B4 &amp; ". " &amp; E4 &amp; ": " &amp; G4</f>
-        <v>2. How books are made: Deconstructing books</v>
+        <f t="shared" si="4"/>
+        <v>2. How books are made</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" ref="L4:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; F4,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-How-books-are-made</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>47</v>
+      <c r="M4" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="N4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -969,14 +996,14 @@
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">3. Excursion: </v>
+        <v>3. Excursion</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -984,10 +1011,10 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1028,27 +1055,27 @@
       </c>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
-        <v>4. Parchment as writing support: Preparing animal skins</v>
+        <v>4. Parchment as writing support</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>4-Parchment-as-writing-support</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1079,6 +1106,10 @@
         <v>21</v>
       </c>
       <c r="H7" s="16"/>
+      <c r="I7" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>. Ascension (no class)</v>
+      </c>
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1106,27 +1137,27 @@
       </c>
       <c r="I8" t="str">
         <f t="shared" si="4"/>
-        <v>5. Papyrus &amp; paper as writing support: Preparing plant materials</v>
+        <v>5. Papyrus &amp; paper as writing support</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>5-Papyrus-paper-as-writing-support</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1167,27 +1198,27 @@
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>6. Binding &amp; Layout: Arranging pages and spaces</v>
+        <v>6. Binding &amp; Layout</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>6-Binding-Layout</v>
       </c>
-      <c r="M9" s="21" t="s">
-        <v>49</v>
+      <c r="M9" s="22" t="s">
+        <v>48</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1217,6 +1248,10 @@
       <c r="F10" s="16" t="s">
         <v>22</v>
       </c>
+      <c r="I10" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>. Corpus Christi (no class)</v>
+      </c>
       <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1238,22 +1273,25 @@
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">7. Excursion: </v>
+        <v>7. Excursion</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
         <v>7-Excursion</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1294,27 +1332,27 @@
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
-        <v>8. Inks &amp; Utensils: Mixing and writing</v>
+        <v>8. Inks &amp; Utensils</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>8-Inks-Utensils</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1355,27 +1393,25 @@
       </c>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
-        <v>9. Paratexts: Adding headers, decorations, and annotations</v>
+        <v>9. Paratexts</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>9-Paratexts</v>
       </c>
-      <c r="M13" s="21" t="s">
-        <v>47</v>
-      </c>
+      <c r="M13" s="21"/>
       <c r="N13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1410,14 +1446,14 @@
       </c>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">10. Presentations: </v>
+        <v>10. Presentations</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -1425,10 +1461,10 @@
       </c>
       <c r="M14" s="11"/>
       <c r="N14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1463,14 +1499,14 @@
       </c>
       <c r="I15" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">11. Review: </v>
+        <v>11. Review</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -1478,10 +1514,10 @@
       </c>
       <c r="M15" s="9"/>
       <c r="N15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D010587A-D445-D543-B783-C387F3428A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA19F91E-C840-2C49-A683-E025023C18A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" hidden="1" customWidth="1"/>
@@ -989,32 +989,38 @@
         <v>2025-05-15-3.md</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
-        <v>3. Excursion</v>
+        <v>3. Parchment as writing support</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
-        <v>3-Excursion</v>
+        <v>3-Parchment-as-writing-support</v>
       </c>
       <c r="M5" s="11"/>
-      <c r="N5" t="s">
-        <v>51</v>
+      <c r="N5" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="O5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1042,40 +1048,35 @@
         <v>2025-05-22-4.md</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
-        <v>4. Parchment as writing support</v>
+        <v>4. Excursion</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
-        <v>4-Parchment-as-writing-support</v>
+        <v>4-Excursion</v>
       </c>
       <c r="M6" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="12" t="s">
-        <v>56</v>
+      <c r="N6" t="s">
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1536,8 +1537,13 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="5:14" x14ac:dyDescent="0.2">
+      <c r="E18" s="19"/>
+      <c r="F18" s="4"/>
+      <c r="N18" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA19F91E-C840-2C49-A683-E025023C18A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA00E40-1A26-4647-9AAC-AEF819BE5C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
   <si>
     <t>blank</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>[gruendlerIntroduction2020, vallejomoreuBooksSkinDetectives2023]</t>
+  </si>
+  <si>
+    <t>businessinsiderHowAnimalHides2021, businessinsiderHowJudaismsMost2024, maniaci11MaterialsTools2015</t>
   </si>
 </sst>
 </file>
@@ -297,9 +300,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -398,20 +408,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -421,35 +431,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1069,8 +1080,8 @@
         <f t="shared" si="5"/>
         <v>4-Excursion</v>
       </c>
-      <c r="M6" s="21" t="s">
-        <v>47</v>
+      <c r="M6" s="23" t="s">
+        <v>83</v>
       </c>
       <c r="N6" t="s">
         <v>51</v>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA00E40-1A26-4647-9AAC-AEF819BE5C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8948FE-51DD-A143-986B-0397CFC0F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>blank</t>
   </si>
@@ -174,12 +174,6 @@
   </si>
   <si>
     <t>quiring, quire and folio numbers, ruling, pricking, VisColl</t>
-  </si>
-  <si>
-    <t>ComSt handbook, YT video</t>
-  </si>
-  <si>
-    <t>ComST handbook?</t>
   </si>
   <si>
     <t>ComSt handbook</t>
@@ -289,6 +283,9 @@
   </si>
   <si>
     <t>businessinsiderHowAnimalHides2021, businessinsiderHowJudaismsMost2024, maniaci11MaterialsTools2015</t>
+  </si>
+  <si>
+    <t>businessinsiderMeetLastPapyrus2021, gibsonPapermakingCottonPulp2025, robertc.williamsmuseumofpapermakingHistoryPapermakingWorld, universityofiowagraduatecollegeChanceryPapermaking201620002016</t>
   </si>
 </sst>
 </file>
@@ -876,14 +873,14 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Introduction</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -959,20 +956,20 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" ref="L4:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; F4,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-How-books-are-made</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1020,7 +1017,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -1028,10 +1025,10 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1074,20 +1071,20 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>4-Excursion</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1156,20 +1153,20 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>5-Papyrus-paper-as-writing-support</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1217,20 +1214,18 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>6-Binding-Layout</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>48</v>
-      </c>
+      <c r="M9" s="22"/>
       <c r="N9" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1292,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -1300,10 +1295,10 @@
       </c>
       <c r="M11" s="11"/>
       <c r="N11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1351,20 +1346,20 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>8-Inks-Utensils</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1412,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
@@ -1420,10 +1415,10 @@
       </c>
       <c r="M13" s="21"/>
       <c r="N13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1465,7 +1460,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -1473,10 +1468,10 @@
       </c>
       <c r="M14" s="11"/>
       <c r="N14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1518,7 +1513,7 @@
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -1526,10 +1521,10 @@
       </c>
       <c r="M15" s="9"/>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8948FE-51DD-A143-986B-0397CFC0F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E95ACDB-FEF8-974D-BD09-214FF591BA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>quiring, quire and folio numbers, ruling, pricking, VisColl</t>
   </si>
   <si>
-    <t>ComSt handbook</t>
-  </si>
-  <si>
     <t>1. Determine your own goals for the course.
 2. Begin to consider the physical aspects involved in writing, transmitting, and reading scripture.</t>
   </si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>businessinsiderMeetLastPapyrus2021, gibsonPapermakingCottonPulp2025, robertc.williamsmuseumofpapermakingHistoryPapermakingWorld, universityofiowagraduatecollegeChanceryPapermaking201620002016</t>
+  </si>
+  <si>
+    <t>rabinMaterialStudiesHistoric2021</t>
   </si>
 </sst>
 </file>
@@ -297,9 +297,16 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -405,20 +412,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -428,35 +435,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -873,14 +881,14 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>1-Introduction</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P2" t="str">
         <f t="shared" ref="P2:P15" si="2">"["&amp;B2&amp;"]"</f>
@@ -956,20 +964,20 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" ref="L4:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; F4,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-How-books-are-made</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P4" t="str">
         <f t="shared" si="2"/>
@@ -1017,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -1025,10 +1033,10 @@
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P5" t="str">
         <f t="shared" si="2"/>
@@ -1071,20 +1079,20 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>4-Excursion</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P6" t="str">
         <f t="shared" si="2"/>
@@ -1153,20 +1161,20 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>5-Papyrus-paper-as-writing-support</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P8" t="str">
         <f t="shared" si="2"/>
@@ -1194,38 +1202,40 @@
         <v>2025-06-12-6.md</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>6. Binding &amp; Layout</v>
+        <v>6. Inks &amp; Utensils</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
-        <v>6-Binding-Layout</v>
-      </c>
-      <c r="M9" s="22"/>
-      <c r="N9" s="12" t="s">
-        <v>55</v>
+        <v>6-Inks-Utensils</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" t="s">
+        <v>52</v>
       </c>
       <c r="O9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1287,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -1295,10 +1305,10 @@
       </c>
       <c r="M11" s="11"/>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1326,40 +1336,38 @@
         <v>2025-07-03-8.md</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
-        <v>8. Inks &amp; Utensils</v>
+        <v>8. Binding &amp; Layout</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
-        <v>8-Inks-Utensils</v>
-      </c>
-      <c r="M12" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" t="s">
-        <v>53</v>
+        <v>8-Binding-Layout</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1407,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
@@ -1415,10 +1423,10 @@
       </c>
       <c r="M13" s="21"/>
       <c r="N13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1460,7 +1468,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -1468,10 +1476,10 @@
       </c>
       <c r="M14" s="11"/>
       <c r="N14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1513,7 +1521,7 @@
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -1521,10 +1529,10 @@
       </c>
       <c r="M15" s="9"/>
       <c r="N15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
@@ -1544,7 +1552,9 @@
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:14" x14ac:dyDescent="0.2">
-      <c r="E17" s="4"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="4"/>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" spans="5:14" x14ac:dyDescent="0.2">
       <c r="E18" s="19"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E95ACDB-FEF8-974D-BD09-214FF591BA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CA96B4-4FDC-F74C-B851-C81DB40F4F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="84">
   <si>
     <t>blank</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>rabinMaterialStudiesHistoric2021</t>
+  </si>
+  <si>
+    <t>FAQ, Examples, and Tools</t>
   </si>
 </sst>
 </file>
@@ -1283,14 +1286,14 @@
         <v>2025-06-26-7.md</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>29</v>
+        <v>83</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>7. Excursion</v>
+        <v>7. FAQ, Examples, and Tools</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
@@ -1301,7 +1304,7 @@
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
-        <v>7-Excursion</v>
+        <v>7-FAQ,-Examples,-and-Tools</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" t="s">

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CA96B4-4FDC-F74C-B851-C81DB40F4F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14757D5-12D3-B64D-AF51-5A34C31746F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
   <si>
     <t>blank</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Practice the steps of papyrus making or paper making using your own materials.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sew or collate pages and mark the writing space. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Record in-depth observations and questions about the production of 1 manuscript or printed book. </t>
   </si>
   <si>
@@ -289,6 +286,12 @@
   </si>
   <si>
     <t>FAQ, Examples, and Tools</t>
+  </si>
+  <si>
+    <t>maniaci13MakingCodex2015</t>
+  </si>
+  <si>
+    <t>Use a chainstitch to sew together 4 or more quires. If you have time, also rule a page using one of the ruling techniques.</t>
   </si>
 </sst>
 </file>
@@ -884,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -967,14 +970,14 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" ref="L4:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; F4,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-How-books-are-made</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
         <v>50</v>
@@ -1028,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -1082,14 +1085,14 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>4-Excursion</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N6" t="s">
         <v>48</v>
@@ -1164,14 +1167,14 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>5-Papyrus-paper-as-writing-support</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>49</v>
@@ -1225,20 +1228,20 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>6-Inks-Utensils</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N9" t="s">
         <v>52</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P9" t="str">
         <f t="shared" si="2"/>
@@ -1286,10 +1289,10 @@
         <v>2025-06-26-7.md</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -1300,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -1311,7 +1314,7 @@
         <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P11" t="str">
         <f t="shared" si="2"/>
@@ -1359,18 +1362,20 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>8-Binding-Layout</v>
       </c>
-      <c r="M12" s="21"/>
+      <c r="M12" s="21" t="s">
+        <v>83</v>
+      </c>
       <c r="N12" s="12" t="s">
         <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1418,7 +1423,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
@@ -1429,7 +1434,7 @@
         <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1471,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -1482,7 +1487,7 @@
         <v>57</v>
       </c>
       <c r="O14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1524,7 +1529,7 @@
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -1535,7 +1540,7 @@
         <v>56</v>
       </c>
       <c r="O15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25scripture/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14757D5-12D3-B64D-AF51-5A34C31746F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48183B73-470C-2E45-8A84-CB4035890812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="86">
   <si>
     <t>blank</t>
   </si>
@@ -231,9 +231,6 @@
     <t>Mix your own ink and write on your sample manuscript with your own utensil.</t>
   </si>
   <si>
-    <t>Add paratexts of different types to your sample manuscript.</t>
-  </si>
-  <si>
     <t>Present the manuscript you created, explaining the decisions you made about its production and the challenges you faced.</t>
   </si>
   <si>
@@ -292,6 +289,12 @@
   </si>
   <si>
     <t>Use a chainstitch to sew together 4 or more quires. If you have time, also rule a page using one of the ruling techniques.</t>
+  </si>
+  <si>
+    <t>derocheEvidenceHistoryManuscript2005</t>
+  </si>
+  <si>
+    <t>On a regular A4 sheet of paper, mark the places on the page where at least 5 different types of paratexts of your choice might occur: e.g., title, preface, rubrics, ownership note, marginalia, colophon.</t>
   </si>
 </sst>
 </file>
@@ -887,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B2 &amp; ". " &amp; F2,".",""),"&amp;","")," ","-"),"--","-")</f>
@@ -970,14 +973,14 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" ref="L4:L15" si="5">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4 &amp; ". " &amp; F4,".",""),"&amp;","")," ","-"),"--","-")</f>
         <v>2-How-books-are-made</v>
       </c>
       <c r="M4" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N4" t="s">
         <v>50</v>
@@ -1031,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -1085,14 +1088,14 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>4-Excursion</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s">
         <v>48</v>
@@ -1167,14 +1170,14 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
         <v>5-Papyrus-paper-as-writing-support</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>49</v>
@@ -1228,14 +1231,14 @@
         <v>6</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
         <v>6-Inks-Utensils</v>
       </c>
       <c r="M9" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
         <v>52</v>
@@ -1289,10 +1292,10 @@
         <v>2025-06-26-7.md</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
@@ -1303,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -1362,20 +1365,20 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
         <v>8-Binding-Layout</v>
       </c>
       <c r="M12" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N12" s="12" t="s">
         <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P12" t="str">
         <f t="shared" si="2"/>
@@ -1423,18 +1426,20 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
         <v>9-Paratexts</v>
       </c>
-      <c r="M13" s="21"/>
+      <c r="M13" s="21" t="s">
+        <v>84</v>
+      </c>
       <c r="N13" t="s">
         <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="P13" t="str">
         <f t="shared" si="2"/>
@@ -1476,7 +1481,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -1487,7 +1492,7 @@
         <v>57</v>
       </c>
       <c r="O14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P14" t="str">
         <f t="shared" si="2"/>
@@ -1529,7 +1534,7 @@
         <v>11</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -1540,7 +1545,7 @@
         <v>56</v>
       </c>
       <c r="O15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P15" t="str">
         <f t="shared" si="2"/>
